--- a/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
@@ -504,7 +504,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -854,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
@@ -70,19 +70,19 @@
     <t>Jogo 3 (JG3)</t>
   </si>
   <si>
+    <t>AZURRA82</t>
+  </si>
+  <si>
     <t>FÚRIA LEON</t>
   </si>
   <si>
-    <t>AZURRA82</t>
-  </si>
-  <si>
     <t>Jogo 4 (JG4)</t>
   </si>
   <si>
+    <t>Mau Humor F.C.</t>
+  </si>
+  <si>
     <t>Grêmio imortal 37</t>
-  </si>
-  <si>
-    <t>Mau Humor F.C.</t>
   </si>
 </sst>
 </file>
@@ -483,10 +483,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -495,13 +495,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>55.05</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>37.83</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>17.22</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -524,16 +524,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>37.83</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>55.05</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-17.22</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -589,22 +589,22 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -621,22 +621,22 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -695,10 +695,10 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>43.82</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>43.73</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.09000000000000341</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -736,16 +736,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>43.73</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>43.82</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-0.09000000000000341</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -801,10 +801,10 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -813,13 +813,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>67.55</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.7999999999999972</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -842,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>67.55</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-0.7999999999999972</v>
       </c>
       <c r="J3">
         <v>2</v>

--- a/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
@@ -495,13 +495,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>55.05</v>
+        <v>55.050048828125</v>
       </c>
       <c r="H2">
-        <v>37.83</v>
+        <v>37.830078125</v>
       </c>
       <c r="I2">
-        <v>17.22</v>
+        <v>17.219970703125</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -527,13 +527,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>37.83</v>
+        <v>37.830078125</v>
       </c>
       <c r="H3">
-        <v>55.05</v>
+        <v>55.050048828125</v>
       </c>
       <c r="I3">
-        <v>-17.22</v>
+        <v>-17.219970703125</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
       <c r="H2">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -633,10 +633,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
       <c r="H3">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>43.82</v>
+        <v>43.820068359375</v>
       </c>
       <c r="H2">
-        <v>43.73</v>
+        <v>43.72998046875</v>
       </c>
       <c r="I2">
-        <v>0.09000000000000341</v>
+        <v>0.090087890625</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>43.73</v>
+        <v>43.72998046875</v>
       </c>
       <c r="H3">
-        <v>43.82</v>
+        <v>43.820068359375</v>
       </c>
       <c r="I3">
-        <v>-0.09000000000000341</v>
+        <v>-0.090087890625</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -813,13 +813,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>68.34999999999999</v>
+        <v>68.35009765625</v>
       </c>
       <c r="H2">
-        <v>67.55</v>
+        <v>67.5498046875</v>
       </c>
       <c r="I2">
-        <v>0.7999999999999972</v>
+        <v>0.80029296875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -845,13 +845,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>67.55</v>
+        <v>67.5498046875</v>
       </c>
       <c r="H3">
-        <v>68.34999999999999</v>
+        <v>68.35009765625</v>
       </c>
       <c r="I3">
-        <v>-0.7999999999999972</v>
+        <v>-0.80029296875</v>
       </c>
       <c r="J3">
         <v>2</v>

--- a/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
@@ -61,28 +61,28 @@
     <t>Jogo 2 (JG2)</t>
   </si>
   <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
     <t>dasdoresfc</t>
   </si>
   <si>
-    <t>JV5 Tricolor Gaúcho</t>
-  </si>
-  <si>
     <t>Jogo 3 (JG3)</t>
   </si>
   <si>
+    <t>FÚRIA LEON</t>
+  </si>
+  <si>
     <t>AZURRA82</t>
   </si>
   <si>
-    <t>FÚRIA LEON</t>
-  </si>
-  <si>
     <t>Jogo 4 (JG4)</t>
   </si>
   <si>
+    <t>Grêmio imortal 37</t>
+  </si>
+  <si>
     <t>Mau Humor F.C.</t>
-  </si>
-  <si>
-    <t>Grêmio imortal 37</t>
   </si>
 </sst>
 </file>
@@ -483,10 +483,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -495,13 +495,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>55.050048828125</v>
+        <v>130.930048828125</v>
       </c>
       <c r="H2">
-        <v>37.830078125</v>
+        <v>94.76007812500001</v>
       </c>
       <c r="I2">
-        <v>17.219970703125</v>
+        <v>36.16997070312499</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -524,16 +524,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>37.830078125</v>
+        <v>94.76007812500001</v>
       </c>
       <c r="H3">
-        <v>55.050048828125</v>
+        <v>130.930048828125</v>
       </c>
       <c r="I3">
-        <v>-17.219970703125</v>
+        <v>-36.16997070312499</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -589,10 +589,10 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -601,13 +601,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>55.89990234375</v>
+        <v>159.28990234375</v>
       </c>
       <c r="H2">
-        <v>55.89990234375</v>
+        <v>138.14990234375</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>21.13999999999999</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -630,16 +630,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>55.89990234375</v>
+        <v>138.14990234375</v>
       </c>
       <c r="H3">
-        <v>55.89990234375</v>
+        <v>159.28990234375</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-21.13999999999999</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -704,16 +704,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>43.820068359375</v>
+        <v>110.30998046875</v>
       </c>
       <c r="H2">
-        <v>43.72998046875</v>
+        <v>103.430068359375</v>
       </c>
       <c r="I2">
-        <v>0.090087890625</v>
+        <v>6.879912109374999</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -727,10 +727,10 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>43.72998046875</v>
+        <v>103.430068359375</v>
       </c>
       <c r="H3">
-        <v>43.820068359375</v>
+        <v>110.30998046875</v>
       </c>
       <c r="I3">
-        <v>-0.090087890625</v>
+        <v>-6.879912109374999</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -810,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>68.35009765625</v>
+        <v>156.2298046875</v>
       </c>
       <c r="H2">
-        <v>67.5498046875</v>
+        <v>142.63009765625</v>
       </c>
       <c r="I2">
-        <v>0.80029296875</v>
+        <v>13.59970703125001</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -833,10 +833,10 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>67.5498046875</v>
+        <v>142.63009765625</v>
       </c>
       <c r="H3">
-        <v>68.35009765625</v>
+        <v>156.2298046875</v>
       </c>
       <c r="I3">
-        <v>-0.80029296875</v>
+        <v>-13.59970703125001</v>
       </c>
       <c r="J3">
         <v>2</v>

--- a/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_classificacao_por_jogo_quartas_sula.xlsx
@@ -495,13 +495,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>130.930048828125</v>
+        <v>130.929931640625</v>
       </c>
       <c r="H2">
-        <v>94.76007812500001</v>
+        <v>94.760009765625</v>
       </c>
       <c r="I2">
-        <v>36.16997070312499</v>
+        <v>36.169921875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -527,13 +527,13 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>94.76007812500001</v>
+        <v>94.760009765625</v>
       </c>
       <c r="H3">
-        <v>130.930048828125</v>
+        <v>130.929931640625</v>
       </c>
       <c r="I3">
-        <v>-36.16997070312499</v>
+        <v>-36.169921875</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -601,13 +601,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>159.28990234375</v>
+        <v>159.2900390625</v>
       </c>
       <c r="H2">
         <v>138.14990234375</v>
       </c>
       <c r="I2">
-        <v>21.13999999999999</v>
+        <v>21.14013671875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -636,10 +636,10 @@
         <v>138.14990234375</v>
       </c>
       <c r="H3">
-        <v>159.28990234375</v>
+        <v>159.2900390625</v>
       </c>
       <c r="I3">
-        <v>-21.13999999999999</v>
+        <v>-21.14013671875</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -707,13 +707,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>110.30998046875</v>
+        <v>110.31005859375</v>
       </c>
       <c r="H2">
-        <v>103.430068359375</v>
+        <v>103.43017578125</v>
       </c>
       <c r="I2">
-        <v>6.879912109374999</v>
+        <v>6.8798828125</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>103.430068359375</v>
+        <v>103.43017578125</v>
       </c>
       <c r="H3">
-        <v>110.30998046875</v>
+        <v>110.31005859375</v>
       </c>
       <c r="I3">
-        <v>-6.879912109374999</v>
+        <v>-6.8798828125</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -813,13 +813,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>156.2298046875</v>
+        <v>156.22998046875</v>
       </c>
       <c r="H2">
-        <v>142.63009765625</v>
+        <v>142.6298828125</v>
       </c>
       <c r="I2">
-        <v>13.59970703125001</v>
+        <v>13.60009765625</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -845,13 +845,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>142.63009765625</v>
+        <v>142.6298828125</v>
       </c>
       <c r="H3">
-        <v>156.2298046875</v>
+        <v>156.22998046875</v>
       </c>
       <c r="I3">
-        <v>-13.59970703125001</v>
+        <v>-13.60009765625</v>
       </c>
       <c r="J3">
         <v>2</v>
